--- a/docs/excel_templates/SizingSummary.xlsx
+++ b/docs/excel_templates/SizingSummary.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Velocity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Slope" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,7 +533,6 @@
           <t>DN50</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,7 +558,78 @@
           <t>DN150</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Installed Size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Upstream Invert (m)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Downstream Invert (m)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Run Length (m)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MH-01 to MH-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>150mm</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>981.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>980.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sample row, sanity-checked at 1.83% (&gt;=1.04% min for this diameter).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/excel_templates/SizingSummary.xlsx
+++ b/docs/excel_templates/SizingSummary.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Velocity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Slope" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EquipmentSizing" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,4 +635,86 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Required (Calc)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Installed (Drawing)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tolerance (%)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SP-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Flow (L/s)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>L/s</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sample row using a real project's own numbers (F12-04-233, docs/PROCEDURE.md #17/#18): calc sheet requires 0.06 L/s, the P0801 pumps schedule shows 0.30 L/s installed -- passes here since installed exceeds required, but the 5x gap between the two sources is itself worth a human look.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/excel_templates/SizingSummary.xlsx
+++ b/docs/excel_templates/SizingSummary.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Velocity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Slope" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="EquipmentSizing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Manholes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,4 +718,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MH Size (mm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Approx Depth (m)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MH-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>600X600</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sample row using a real project's own numbers (F12-04-233, docs/PROCEDURE.md #22): P0801 SEWAGE MANHOLES SCHEDULE, square inspection chamber. At 0.6m depth this matches the 0-0.6m tier (min side 100mm) -- 600mm passes comfortably.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>